--- a/data.mn/public/datasets/hospital-beds-national-mn.xlsx
+++ b/data.mn/public/datasets/hospital-beds-national-mn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -716,6 +720,14 @@
         <v>30117</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B38" t="n">
+        <v>29465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
